--- a/เอกสารและรายชื่อคณะสีแสด_ปี69/แยกฝ่าย/สแตนเชียร์/รายชื่อฝ่ายสแตนเชียร์_คณะสีแสด_ปี69.xlsx
+++ b/เอกสารและรายชื่อคณะสีแสด_ปี69/แยกฝ่าย/สแตนเชียร์/รายชื่อฝ่ายสแตนเชียร์_คณะสีแสด_ปี69.xlsx
@@ -11,12 +11,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="525" uniqueCount="205">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="435" uniqueCount="189">
   <si>
     <t>📣 รายชื่อสมาชิกฝ่ายสแตนเชียร์ — คณะสีแสด (สีบุษราคัม) ปี 2569</t>
   </si>
   <si>
-    <t>จำนวนสมาชิกทั้งหมด 85 คน (ชาย 44 / หญิง 41 | ระดับชั้น ม.1) | การแข่งขันกีฬาสีภายใน ประจำปีการศึกษา 2569</t>
+    <t>จำนวนสมาชิกทั้งหมด 84 คน (ชาย 43 / หญิง 41 | ระดับชั้น ม.1) | การแข่งขันกีฬาสีภายใน ประจำปีการศึกษา 2569</t>
   </si>
   <si>
     <t>ลำดับ</t>
@@ -43,9 +43,6 @@
     <t>เบอร์โทรศัพท์</t>
   </si>
   <si>
-    <t>ม.1/1</t>
-  </si>
-  <si>
     <t>34890</t>
   </si>
   <si>
@@ -100,9 +97,6 @@
     <t>เด็กหญิงสุกัญญา กันทาวงศ์</t>
   </si>
   <si>
-    <t>ม.1/2</t>
-  </si>
-  <si>
     <t>34932</t>
   </si>
   <si>
@@ -151,13 +145,10 @@
     <t>085-226-6457</t>
   </si>
   <si>
-    <t>ม.1/3</t>
-  </si>
-  <si>
     <t>34974</t>
   </si>
   <si>
-    <t>เด็กชายธีระ</t>
+    <t>เด็กชายธีระ -</t>
   </si>
   <si>
     <t>34980</t>
@@ -190,9 +181,6 @@
     <t>เด็กหญิงวันวิสา สังเกตุ</t>
   </si>
   <si>
-    <t>ม.1/4</t>
-  </si>
-  <si>
     <t>35010</t>
   </si>
   <si>
@@ -235,9 +223,6 @@
     <t>เด็กหญิงอมลรดา ประสิทธิ์จำเนียร</t>
   </si>
   <si>
-    <t>ม.1/5</t>
-  </si>
-  <si>
     <t>35052</t>
   </si>
   <si>
@@ -265,7 +250,7 @@
     <t>35076</t>
   </si>
   <si>
-    <t>เด็กหญิงนาซาลิน</t>
+    <t>เด็กหญิงนาซาลิน -</t>
   </si>
   <si>
     <t>35082</t>
@@ -283,15 +268,6 @@
     <t>วอลเลย์บอล, สแตนเชียร์</t>
   </si>
   <si>
-    <t>ม.1/6</t>
-  </si>
-  <si>
-    <t>34469</t>
-  </si>
-  <si>
-    <t>เด็กชายจิรสิน ขันทะ</t>
-  </si>
-  <si>
     <t>35094</t>
   </si>
   <si>
@@ -328,9 +304,6 @@
     <t>เด็กหญิงรัตนากร ทองแม้น</t>
   </si>
   <si>
-    <t>ม.1/7</t>
-  </si>
-  <si>
     <t>35130</t>
   </si>
   <si>
@@ -373,9 +346,6 @@
     <t>เด็กหญิงอภัสนันท์ นันสุ</t>
   </si>
   <si>
-    <t>ม.1/8</t>
-  </si>
-  <si>
     <t>35172</t>
   </si>
   <si>
@@ -403,7 +373,7 @@
     <t>35196</t>
   </si>
   <si>
-    <t>เด็กหญิงณัฐธิดา</t>
+    <t>เด็กหญิงณัฐธิดา -</t>
   </si>
   <si>
     <t>35202</t>
@@ -418,9 +388,6 @@
     <t>เด็กหญิงไอวริน ตาละสา</t>
   </si>
   <si>
-    <t>ม.1/9</t>
-  </si>
-  <si>
     <t>35214</t>
   </si>
   <si>
@@ -460,9 +427,6 @@
     <t>เด็กหญิงวัฒนวดี เนียมโห้</t>
   </si>
   <si>
-    <t>ม.1/10</t>
-  </si>
-  <si>
     <t>35250</t>
   </si>
   <si>
@@ -493,9 +457,6 @@
     <t>เด็กหญิงชนมน จันตา</t>
   </si>
   <si>
-    <t>ม.1/11</t>
-  </si>
-  <si>
     <t>35280</t>
   </si>
   <si>
@@ -526,9 +487,6 @@
     <t>เด็กหญิงภาสินี ชอบขาย</t>
   </si>
   <si>
-    <t>ม.1/12</t>
-  </si>
-  <si>
     <t>35310</t>
   </si>
   <si>
@@ -559,9 +517,6 @@
     <t>เด็กหญิงภัคศิญา ก้องพนาไพรสณฑ์</t>
   </si>
   <si>
-    <t>ม.1/13</t>
-  </si>
-  <si>
     <t>35340</t>
   </si>
   <si>
@@ -589,10 +544,7 @@
     <t>35364</t>
   </si>
   <si>
-    <t>เด็กหญิงอัมรา</t>
-  </si>
-  <si>
-    <t>ม.1/14</t>
+    <t>เด็กหญิงอัมรา -</t>
   </si>
   <si>
     <t>35370</t>
@@ -604,7 +556,7 @@
     <t>35376</t>
   </si>
   <si>
-    <t>เด็กชายภควัตร</t>
+    <t>เด็กชายภควัตร -</t>
   </si>
   <si>
     <t>35382</t>
@@ -622,7 +574,7 @@
     <t>รวมสมาชิกฝ่ายสแตนเชียร์ทั้งหมด</t>
   </si>
   <si>
-    <t>85 คน (ชาย 44 / หญิง 41)</t>
+    <t>84 คน (ชาย 43 / หญิง 41)</t>
   </si>
   <si>
     <t/>
@@ -1120,7 +1072,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H89"/>
+  <dimension ref="A1:H88"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -1186,2237 +1138,2043 @@
       <c r="A4" s="4">
         <v>1</v>
       </c>
-      <c r="B4" s="4" t="s">
-        <v>10</v>
-      </c>
+      <c r="B4" s="4"/>
       <c r="C4" s="4">
         <v>2</v>
       </c>
       <c r="D4" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="E4" s="5" t="s">
-        <v>12</v>
-      </c>
       <c r="F4" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="7">
         <v>2</v>
       </c>
-      <c r="B5" s="7" t="s">
-        <v>10</v>
-      </c>
+      <c r="B5" s="7"/>
       <c r="C5" s="7">
         <v>8</v>
       </c>
       <c r="D5" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="E5" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="E5" s="8" t="s">
-        <v>17</v>
-      </c>
       <c r="F5" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G5" s="9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H5" s="7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="4">
         <v>3</v>
       </c>
-      <c r="B6" s="4" t="s">
-        <v>10</v>
-      </c>
+      <c r="B6" s="4"/>
       <c r="C6" s="4">
         <v>14</v>
       </c>
       <c r="D6" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E6" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="E6" s="5" t="s">
-        <v>19</v>
-      </c>
       <c r="F6" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="7">
         <v>4</v>
       </c>
-      <c r="B7" s="7" t="s">
-        <v>10</v>
-      </c>
+      <c r="B7" s="7"/>
       <c r="C7" s="7">
         <v>20</v>
       </c>
       <c r="D7" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="E7" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="E7" s="8" t="s">
-        <v>21</v>
-      </c>
       <c r="F7" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G7" s="9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H7" s="7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="4">
         <v>5</v>
       </c>
-      <c r="B8" s="4" t="s">
-        <v>10</v>
-      </c>
+      <c r="B8" s="4"/>
       <c r="C8" s="4">
         <v>26</v>
       </c>
       <c r="D8" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="E8" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="E8" s="5" t="s">
-        <v>23</v>
-      </c>
       <c r="F8" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="7">
         <v>6</v>
       </c>
-      <c r="B9" s="7" t="s">
-        <v>10</v>
-      </c>
+      <c r="B9" s="7"/>
       <c r="C9" s="7">
         <v>32</v>
       </c>
       <c r="D9" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="E9" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="E9" s="8" t="s">
-        <v>26</v>
-      </c>
       <c r="F9" s="7" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G9" s="9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H9" s="7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="4">
         <v>7</v>
       </c>
-      <c r="B10" s="4" t="s">
-        <v>10</v>
-      </c>
+      <c r="B10" s="4"/>
       <c r="C10" s="4">
         <v>38</v>
       </c>
       <c r="D10" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E10" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="E10" s="5" t="s">
-        <v>28</v>
-      </c>
       <c r="F10" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="7">
         <v>8</v>
       </c>
-      <c r="B11" s="7" t="s">
-        <v>29</v>
-      </c>
+      <c r="B11" s="7"/>
       <c r="C11" s="7">
         <v>4</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G11" s="9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H11" s="7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="4">
         <v>9</v>
       </c>
-      <c r="B12" s="4" t="s">
-        <v>29</v>
-      </c>
+      <c r="B12" s="4"/>
       <c r="C12" s="4">
         <v>10</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="7">
         <v>10</v>
       </c>
-      <c r="B13" s="7" t="s">
-        <v>29</v>
-      </c>
+      <c r="B13" s="7"/>
       <c r="C13" s="7">
         <v>16</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G13" s="9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H13" s="7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="4">
         <v>11</v>
       </c>
-      <c r="B14" s="4" t="s">
-        <v>29</v>
-      </c>
+      <c r="B14" s="4"/>
       <c r="C14" s="4">
         <v>23</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="7">
         <v>12</v>
       </c>
-      <c r="B15" s="7" t="s">
-        <v>29</v>
-      </c>
+      <c r="B15" s="7"/>
       <c r="C15" s="7">
         <v>17</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G15" s="9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H15" s="7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="4">
         <v>13</v>
       </c>
-      <c r="B16" s="4" t="s">
-        <v>29</v>
-      </c>
+      <c r="B16" s="4"/>
       <c r="C16" s="4">
         <v>34</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="17" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="7">
         <v>14</v>
       </c>
-      <c r="B17" s="7" t="s">
-        <v>29</v>
-      </c>
+      <c r="B17" s="7"/>
       <c r="C17" s="7">
         <v>40</v>
       </c>
       <c r="D17" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="E17" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="F17" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="G17" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="E17" s="8" t="s">
+      <c r="H17" s="7" t="s">
         <v>43</v>
-      </c>
-      <c r="F17" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="G17" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="H17" s="7" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="4">
         <v>15</v>
       </c>
-      <c r="B18" s="4" t="s">
-        <v>46</v>
-      </c>
+      <c r="B18" s="4"/>
       <c r="C18" s="4">
         <v>6</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="7">
         <v>16</v>
       </c>
-      <c r="B19" s="7" t="s">
+      <c r="B19" s="7"/>
+      <c r="C19" s="7">
+        <v>12</v>
+      </c>
+      <c r="D19" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="C19" s="7">
-        <v>12</v>
-      </c>
-      <c r="D19" s="7" t="s">
-        <v>49</v>
-      </c>
       <c r="E19" s="8" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G19" s="9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H19" s="7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="4">
         <v>17</v>
       </c>
-      <c r="B20" s="4" t="s">
-        <v>46</v>
-      </c>
+      <c r="B20" s="4"/>
       <c r="C20" s="4">
         <v>18</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H20" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="7">
         <v>18</v>
       </c>
-      <c r="B21" s="7" t="s">
-        <v>46</v>
-      </c>
+      <c r="B21" s="7"/>
       <c r="C21" s="7">
         <v>24</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="E21" s="8" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="F21" s="7" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G21" s="9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H21" s="7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="22" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="4">
         <v>19</v>
       </c>
-      <c r="B22" s="4" t="s">
-        <v>46</v>
-      </c>
+      <c r="B22" s="4"/>
       <c r="C22" s="4">
         <v>30</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H22" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="23" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="7">
         <v>20</v>
       </c>
-      <c r="B23" s="7" t="s">
-        <v>46</v>
-      </c>
+      <c r="B23" s="7"/>
       <c r="C23" s="7">
         <v>36</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="E23" s="8" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="F23" s="7" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G23" s="9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H23" s="7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="24" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="4">
         <v>21</v>
       </c>
-      <c r="B24" s="4" t="s">
-        <v>59</v>
-      </c>
+      <c r="B24" s="4"/>
       <c r="C24" s="4">
         <v>2</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H24" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="25" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="7">
         <v>22</v>
       </c>
-      <c r="B25" s="7" t="s">
-        <v>59</v>
-      </c>
+      <c r="B25" s="7"/>
       <c r="C25" s="7">
         <v>8</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="E25" s="8" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="F25" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G25" s="9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H25" s="7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="26" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="4">
         <v>23</v>
       </c>
-      <c r="B26" s="4" t="s">
-        <v>59</v>
-      </c>
+      <c r="B26" s="4"/>
       <c r="C26" s="4">
         <v>14</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H26" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="27" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" s="7">
         <v>24</v>
       </c>
-      <c r="B27" s="7" t="s">
-        <v>59</v>
-      </c>
+      <c r="B27" s="7"/>
       <c r="C27" s="7">
         <v>20</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="E27" s="8" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="F27" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G27" s="9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H27" s="7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="28" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="4">
         <v>25</v>
       </c>
-      <c r="B28" s="4" t="s">
-        <v>59</v>
-      </c>
+      <c r="B28" s="4"/>
       <c r="C28" s="4">
         <v>26</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H28" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="29" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="7">
         <v>26</v>
       </c>
-      <c r="B29" s="7" t="s">
-        <v>59</v>
-      </c>
+      <c r="B29" s="7"/>
       <c r="C29" s="7">
         <v>32</v>
       </c>
       <c r="D29" s="7" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="E29" s="8" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="F29" s="7" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G29" s="9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H29" s="7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="30" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="4">
         <v>27</v>
       </c>
-      <c r="B30" s="4" t="s">
-        <v>59</v>
-      </c>
+      <c r="B30" s="4"/>
       <c r="C30" s="4">
         <v>38</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H30" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="31" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="7">
         <v>28</v>
       </c>
-      <c r="B31" s="7" t="s">
-        <v>74</v>
-      </c>
+      <c r="B31" s="7"/>
       <c r="C31" s="7">
         <v>4</v>
       </c>
       <c r="D31" s="7" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="E31" s="8" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="F31" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G31" s="9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H31" s="7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="32" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" s="4">
         <v>29</v>
       </c>
-      <c r="B32" s="4" t="s">
-        <v>74</v>
-      </c>
+      <c r="B32" s="4"/>
       <c r="C32" s="4">
         <v>10</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H32" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="33" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" s="7">
         <v>30</v>
       </c>
-      <c r="B33" s="7" t="s">
-        <v>74</v>
-      </c>
+      <c r="B33" s="7"/>
       <c r="C33" s="7">
         <v>16</v>
       </c>
       <c r="D33" s="7" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="E33" s="8" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="F33" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G33" s="9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H33" s="7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="34" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" s="4">
         <v>31</v>
       </c>
-      <c r="B34" s="4" t="s">
-        <v>74</v>
-      </c>
+      <c r="B34" s="4"/>
       <c r="C34" s="4">
         <v>22</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="F34" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H34" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="35" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" s="7">
         <v>32</v>
       </c>
-      <c r="B35" s="7" t="s">
-        <v>74</v>
-      </c>
+      <c r="B35" s="7"/>
       <c r="C35" s="7">
         <v>28</v>
       </c>
       <c r="D35" s="7" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="E35" s="8" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="F35" s="7" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G35" s="9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H35" s="7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="36" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" s="4">
         <v>33</v>
       </c>
-      <c r="B36" s="4" t="s">
-        <v>74</v>
-      </c>
+      <c r="B36" s="4"/>
       <c r="C36" s="4">
         <v>34</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="E36" s="5" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="F36" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H36" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="37" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" s="7">
         <v>34</v>
       </c>
-      <c r="B37" s="7" t="s">
-        <v>74</v>
-      </c>
+      <c r="B37" s="7"/>
       <c r="C37" s="7">
         <v>40</v>
       </c>
       <c r="D37" s="7" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="E37" s="8" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="F37" s="7" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G37" s="9" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="H37" s="7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="38" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" s="4">
         <v>35</v>
       </c>
-      <c r="B38" s="4" t="s">
-        <v>90</v>
-      </c>
+      <c r="B38" s="4"/>
       <c r="C38" s="4">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="F38" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H38" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="39" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" s="7">
         <v>36</v>
       </c>
-      <c r="B39" s="7" t="s">
-        <v>90</v>
-      </c>
+      <c r="B39" s="7"/>
       <c r="C39" s="7">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D39" s="7" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="E39" s="8" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="F39" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G39" s="9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H39" s="7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="40" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" s="4">
         <v>37</v>
       </c>
-      <c r="B40" s="4" t="s">
+      <c r="B40" s="4"/>
+      <c r="C40" s="4">
+        <v>18</v>
+      </c>
+      <c r="D40" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="E40" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="C40" s="4">
-        <v>12</v>
-      </c>
-      <c r="D40" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="E40" s="5" t="s">
-        <v>96</v>
-      </c>
       <c r="F40" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H40" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="41" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" s="7">
         <v>38</v>
       </c>
-      <c r="B41" s="7" t="s">
-        <v>90</v>
-      </c>
+      <c r="B41" s="7"/>
       <c r="C41" s="7">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="D41" s="7" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="E41" s="8" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="F41" s="7" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="G41" s="9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H41" s="7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="42" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" s="4">
         <v>39</v>
       </c>
-      <c r="B42" s="4" t="s">
-        <v>90</v>
-      </c>
+      <c r="B42" s="4"/>
       <c r="C42" s="4">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="E42" s="5" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="F42" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H42" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="43" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" s="7">
         <v>40</v>
       </c>
-      <c r="B43" s="7" t="s">
-        <v>90</v>
-      </c>
+      <c r="B43" s="7"/>
       <c r="C43" s="7">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="D43" s="7" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="E43" s="8" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="F43" s="7" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G43" s="9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H43" s="7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="44" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" s="4">
         <v>41</v>
       </c>
-      <c r="B44" s="4" t="s">
-        <v>90</v>
-      </c>
+      <c r="B44" s="4"/>
       <c r="C44" s="4">
-        <v>36</v>
+        <v>2</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="E44" s="5" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="F44" s="4" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H44" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="45" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" s="7">
         <v>42</v>
       </c>
-      <c r="B45" s="7" t="s">
-        <v>105</v>
-      </c>
+      <c r="B45" s="7"/>
       <c r="C45" s="7">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D45" s="7" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="E45" s="8" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="F45" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G45" s="9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H45" s="7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="46" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" s="4">
         <v>43</v>
       </c>
-      <c r="B46" s="4" t="s">
-        <v>105</v>
-      </c>
+      <c r="B46" s="4"/>
       <c r="C46" s="4">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="E46" s="5" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="F46" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H46" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="47" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" s="7">
         <v>44</v>
       </c>
-      <c r="B47" s="7" t="s">
-        <v>105</v>
-      </c>
+      <c r="B47" s="7"/>
       <c r="C47" s="7">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="D47" s="7" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="E47" s="8" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="F47" s="7" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="G47" s="9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H47" s="7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="48" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" s="4">
         <v>45</v>
       </c>
-      <c r="B48" s="4" t="s">
+      <c r="B48" s="4"/>
+      <c r="C48" s="4">
+        <v>26</v>
+      </c>
+      <c r="D48" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="C48" s="4">
-        <v>20</v>
-      </c>
-      <c r="D48" s="4" t="s">
-        <v>112</v>
-      </c>
       <c r="E48" s="5" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="F48" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H48" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="49" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" s="7">
         <v>46</v>
       </c>
-      <c r="B49" s="7" t="s">
-        <v>105</v>
-      </c>
+      <c r="B49" s="7"/>
       <c r="C49" s="7">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="D49" s="7" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="E49" s="8" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="F49" s="7" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G49" s="9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H49" s="7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="50" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" s="4">
         <v>47</v>
       </c>
-      <c r="B50" s="4" t="s">
-        <v>105</v>
-      </c>
+      <c r="B50" s="4"/>
       <c r="C50" s="4">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="D50" s="4" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="E50" s="5" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="F50" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H50" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="51" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" s="7">
         <v>48</v>
       </c>
-      <c r="B51" s="7" t="s">
-        <v>105</v>
-      </c>
+      <c r="B51" s="7"/>
       <c r="C51" s="7">
-        <v>38</v>
+        <v>4</v>
       </c>
       <c r="D51" s="7" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="E51" s="8" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="F51" s="7" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="G51" s="9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H51" s="7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="52" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" s="4">
         <v>49</v>
       </c>
-      <c r="B52" s="4" t="s">
-        <v>120</v>
-      </c>
+      <c r="B52" s="4"/>
       <c r="C52" s="4">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D52" s="4" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="E52" s="5" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="F52" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H52" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="53" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" s="7">
         <v>50</v>
       </c>
-      <c r="B53" s="7" t="s">
-        <v>120</v>
-      </c>
+      <c r="B53" s="7"/>
       <c r="C53" s="7">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D53" s="7" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="E53" s="8" t="s">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="F53" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G53" s="9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H53" s="7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="54" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" s="4">
         <v>51</v>
       </c>
-      <c r="B54" s="4" t="s">
-        <v>120</v>
-      </c>
+      <c r="B54" s="4"/>
       <c r="C54" s="4">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="D54" s="4" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="E54" s="5" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="F54" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H54" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="55" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" s="7">
         <v>52</v>
       </c>
-      <c r="B55" s="7" t="s">
+      <c r="B55" s="7"/>
+      <c r="C55" s="7">
+        <v>28</v>
+      </c>
+      <c r="D55" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="E55" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="C55" s="7">
-        <v>22</v>
-      </c>
-      <c r="D55" s="7" t="s">
-        <v>127</v>
-      </c>
-      <c r="E55" s="8" t="s">
-        <v>128</v>
-      </c>
       <c r="F55" s="7" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="G55" s="9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H55" s="7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="56" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" s="4">
         <v>53</v>
       </c>
-      <c r="B56" s="4" t="s">
-        <v>120</v>
-      </c>
+      <c r="B56" s="4"/>
       <c r="C56" s="4">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D56" s="4" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="E56" s="5" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="F56" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H56" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="57" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" s="7">
         <v>54</v>
       </c>
-      <c r="B57" s="7" t="s">
-        <v>120</v>
-      </c>
+      <c r="B57" s="7"/>
       <c r="C57" s="7">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="D57" s="7" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
       <c r="E57" s="8" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
       <c r="F57" s="7" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G57" s="9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H57" s="7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="58" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" s="4">
         <v>55</v>
       </c>
-      <c r="B58" s="4" t="s">
-        <v>120</v>
-      </c>
+      <c r="B58" s="4"/>
       <c r="C58" s="4">
-        <v>40</v>
+        <v>6</v>
       </c>
       <c r="D58" s="4" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="E58" s="5" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="F58" s="4" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H58" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="59" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" s="7">
         <v>56</v>
       </c>
-      <c r="B59" s="7" t="s">
-        <v>135</v>
-      </c>
+      <c r="B59" s="7"/>
       <c r="C59" s="7">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D59" s="7" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
       <c r="E59" s="8" t="s">
-        <v>137</v>
+        <v>128</v>
       </c>
       <c r="F59" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G59" s="9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H59" s="7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="60" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60" s="4">
         <v>57</v>
       </c>
-      <c r="B60" s="4" t="s">
-        <v>135</v>
-      </c>
+      <c r="B60" s="4"/>
       <c r="C60" s="4">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="D60" s="4" t="s">
-        <v>138</v>
+        <v>129</v>
       </c>
       <c r="E60" s="5" t="s">
-        <v>139</v>
+        <v>130</v>
       </c>
       <c r="F60" s="4" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H60" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="61" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61" s="7">
         <v>58</v>
       </c>
-      <c r="B61" s="7" t="s">
-        <v>135</v>
-      </c>
+      <c r="B61" s="7"/>
       <c r="C61" s="7">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="D61" s="7" t="s">
-        <v>140</v>
+        <v>131</v>
       </c>
       <c r="E61" s="8" t="s">
-        <v>141</v>
+        <v>132</v>
       </c>
       <c r="F61" s="7" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G61" s="9" t="s">
-        <v>14</v>
+        <v>133</v>
       </c>
       <c r="H61" s="7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="62" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62" s="4">
         <v>59</v>
       </c>
-      <c r="B62" s="4" t="s">
+      <c r="B62" s="4"/>
+      <c r="C62" s="4">
+        <v>30</v>
+      </c>
+      <c r="D62" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="E62" s="5" t="s">
         <v>135</v>
       </c>
-      <c r="C62" s="4">
-        <v>24</v>
-      </c>
-      <c r="D62" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="E62" s="5" t="s">
-        <v>143</v>
-      </c>
       <c r="F62" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>144</v>
+        <v>13</v>
       </c>
       <c r="H62" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="63" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63" s="7">
         <v>60</v>
       </c>
-      <c r="B63" s="7" t="s">
-        <v>135</v>
-      </c>
+      <c r="B63" s="7"/>
       <c r="C63" s="7">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="D63" s="7" t="s">
-        <v>145</v>
+        <v>136</v>
       </c>
       <c r="E63" s="8" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="F63" s="7" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G63" s="9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H63" s="7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="64" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64" s="4">
         <v>61</v>
       </c>
-      <c r="B64" s="4" t="s">
-        <v>135</v>
-      </c>
+      <c r="B64" s="4"/>
       <c r="C64" s="4">
-        <v>36</v>
+        <v>2</v>
       </c>
       <c r="D64" s="4" t="s">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="E64" s="5" t="s">
-        <v>148</v>
+        <v>139</v>
       </c>
       <c r="F64" s="4" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H64" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="65" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65" s="7">
         <v>62</v>
       </c>
-      <c r="B65" s="7" t="s">
-        <v>149</v>
-      </c>
+      <c r="B65" s="7"/>
       <c r="C65" s="7">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D65" s="7" t="s">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="E65" s="8" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="F65" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G65" s="9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H65" s="7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="66" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66" s="4">
         <v>63</v>
       </c>
-      <c r="B66" s="4" t="s">
-        <v>149</v>
-      </c>
+      <c r="B66" s="4"/>
       <c r="C66" s="4">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D66" s="4" t="s">
-        <v>152</v>
+        <v>142</v>
       </c>
       <c r="E66" s="5" t="s">
-        <v>153</v>
+        <v>143</v>
       </c>
       <c r="F66" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H66" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="67" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67" s="7">
         <v>64</v>
       </c>
-      <c r="B67" s="7" t="s">
-        <v>149</v>
-      </c>
+      <c r="B67" s="7"/>
       <c r="C67" s="7">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="D67" s="7" t="s">
-        <v>154</v>
+        <v>144</v>
       </c>
       <c r="E67" s="8" t="s">
-        <v>155</v>
+        <v>145</v>
       </c>
       <c r="F67" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G67" s="9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H67" s="7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="68" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68" s="4">
         <v>65</v>
       </c>
-      <c r="B68" s="4" t="s">
-        <v>149</v>
-      </c>
+      <c r="B68" s="4"/>
       <c r="C68" s="4">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="D68" s="4" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
       <c r="E68" s="5" t="s">
-        <v>157</v>
+        <v>147</v>
       </c>
       <c r="F68" s="4" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H68" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="69" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69" s="7">
         <v>66</v>
       </c>
-      <c r="B69" s="7" t="s">
+      <c r="B69" s="7"/>
+      <c r="C69" s="7">
+        <v>2</v>
+      </c>
+      <c r="D69" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="E69" s="8" t="s">
         <v>149</v>
       </c>
-      <c r="C69" s="7">
-        <v>26</v>
-      </c>
-      <c r="D69" s="7" t="s">
-        <v>158</v>
-      </c>
-      <c r="E69" s="8" t="s">
-        <v>159</v>
-      </c>
       <c r="F69" s="7" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="G69" s="9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H69" s="7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="70" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70" s="4">
         <v>67</v>
       </c>
-      <c r="B70" s="4" t="s">
-        <v>160</v>
-      </c>
+      <c r="B70" s="4"/>
       <c r="C70" s="4">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D70" s="4" t="s">
-        <v>161</v>
+        <v>150</v>
       </c>
       <c r="E70" s="5" t="s">
-        <v>162</v>
+        <v>151</v>
       </c>
       <c r="F70" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H70" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="71" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A71" s="7">
         <v>68</v>
       </c>
-      <c r="B71" s="7" t="s">
-        <v>160</v>
-      </c>
+      <c r="B71" s="7"/>
       <c r="C71" s="7">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D71" s="7" t="s">
-        <v>163</v>
+        <v>152</v>
       </c>
       <c r="E71" s="8" t="s">
-        <v>164</v>
+        <v>153</v>
       </c>
       <c r="F71" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G71" s="9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H71" s="7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="72" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A72" s="4">
         <v>69</v>
       </c>
-      <c r="B72" s="4" t="s">
-        <v>160</v>
-      </c>
+      <c r="B72" s="4"/>
       <c r="C72" s="4">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="D72" s="4" t="s">
-        <v>165</v>
+        <v>154</v>
       </c>
       <c r="E72" s="5" t="s">
-        <v>166</v>
+        <v>155</v>
       </c>
       <c r="F72" s="4" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H72" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="73" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A73" s="7">
         <v>70</v>
       </c>
-      <c r="B73" s="7" t="s">
-        <v>160</v>
-      </c>
+      <c r="B73" s="7"/>
       <c r="C73" s="7">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="D73" s="7" t="s">
-        <v>167</v>
+        <v>156</v>
       </c>
       <c r="E73" s="8" t="s">
-        <v>168</v>
+        <v>157</v>
       </c>
       <c r="F73" s="7" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G73" s="9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H73" s="7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="74" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A74" s="4">
         <v>71</v>
       </c>
-      <c r="B74" s="4" t="s">
-        <v>160</v>
-      </c>
+      <c r="B74" s="4"/>
       <c r="C74" s="4">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="D74" s="4" t="s">
-        <v>169</v>
+        <v>158</v>
       </c>
       <c r="E74" s="5" t="s">
-        <v>170</v>
+        <v>159</v>
       </c>
       <c r="F74" s="4" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="G74" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H74" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="75" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A75" s="7">
         <v>72</v>
       </c>
-      <c r="B75" s="7" t="s">
-        <v>171</v>
-      </c>
+      <c r="B75" s="7"/>
       <c r="C75" s="7">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D75" s="7" t="s">
-        <v>172</v>
+        <v>160</v>
       </c>
       <c r="E75" s="8" t="s">
-        <v>173</v>
+        <v>161</v>
       </c>
       <c r="F75" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G75" s="9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H75" s="7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="76" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A76" s="4">
         <v>73</v>
       </c>
-      <c r="B76" s="4" t="s">
-        <v>171</v>
-      </c>
+      <c r="B76" s="4"/>
       <c r="C76" s="4">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D76" s="4" t="s">
-        <v>174</v>
+        <v>162</v>
       </c>
       <c r="E76" s="5" t="s">
-        <v>175</v>
+        <v>163</v>
       </c>
       <c r="F76" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G76" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H76" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="77" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A77" s="7">
         <v>74</v>
       </c>
-      <c r="B77" s="7" t="s">
-        <v>171</v>
-      </c>
+      <c r="B77" s="7"/>
       <c r="C77" s="7">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="D77" s="7" t="s">
-        <v>176</v>
+        <v>164</v>
       </c>
       <c r="E77" s="8" t="s">
-        <v>177</v>
+        <v>165</v>
       </c>
       <c r="F77" s="7" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="G77" s="9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H77" s="7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="78" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A78" s="4">
         <v>75</v>
       </c>
-      <c r="B78" s="4" t="s">
-        <v>171</v>
-      </c>
+      <c r="B78" s="4"/>
       <c r="C78" s="4">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="D78" s="4" t="s">
-        <v>178</v>
+        <v>166</v>
       </c>
       <c r="E78" s="5" t="s">
-        <v>179</v>
+        <v>167</v>
       </c>
       <c r="F78" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G78" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H78" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="79" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A79" s="7">
         <v>76</v>
       </c>
-      <c r="B79" s="7" t="s">
-        <v>171</v>
-      </c>
+      <c r="B79" s="7"/>
       <c r="C79" s="7">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="D79" s="7" t="s">
-        <v>180</v>
+        <v>168</v>
       </c>
       <c r="E79" s="8" t="s">
-        <v>181</v>
+        <v>169</v>
       </c>
       <c r="F79" s="7" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="G79" s="9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H79" s="7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="80" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A80" s="4">
         <v>77</v>
       </c>
-      <c r="B80" s="4" t="s">
-        <v>182</v>
-      </c>
+      <c r="B80" s="4"/>
       <c r="C80" s="4">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D80" s="4" t="s">
-        <v>183</v>
+        <v>170</v>
       </c>
       <c r="E80" s="5" t="s">
-        <v>184</v>
+        <v>171</v>
       </c>
       <c r="F80" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G80" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H80" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="81" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A81" s="7">
         <v>78</v>
       </c>
-      <c r="B81" s="7" t="s">
-        <v>182</v>
-      </c>
+      <c r="B81" s="7"/>
       <c r="C81" s="7">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D81" s="7" t="s">
-        <v>185</v>
+        <v>172</v>
       </c>
       <c r="E81" s="8" t="s">
-        <v>186</v>
+        <v>173</v>
       </c>
       <c r="F81" s="7" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="G81" s="9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H81" s="7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="82" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A82" s="4">
         <v>79</v>
       </c>
-      <c r="B82" s="4" t="s">
-        <v>182</v>
-      </c>
+      <c r="B82" s="4"/>
       <c r="C82" s="4">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="D82" s="4" t="s">
-        <v>187</v>
+        <v>174</v>
       </c>
       <c r="E82" s="5" t="s">
-        <v>188</v>
+        <v>175</v>
       </c>
       <c r="F82" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G82" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H82" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="83" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A83" s="7">
         <v>80</v>
       </c>
-      <c r="B83" s="7" t="s">
-        <v>182</v>
-      </c>
+      <c r="B83" s="7"/>
       <c r="C83" s="7">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="D83" s="7" t="s">
-        <v>189</v>
+        <v>176</v>
       </c>
       <c r="E83" s="8" t="s">
-        <v>190</v>
+        <v>177</v>
       </c>
       <c r="F83" s="7" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G83" s="9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H83" s="7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="84" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A84" s="4">
         <v>81</v>
       </c>
-      <c r="B84" s="4" t="s">
-        <v>182</v>
-      </c>
+      <c r="B84" s="4"/>
       <c r="C84" s="4">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="D84" s="4" t="s">
-        <v>191</v>
+        <v>178</v>
       </c>
       <c r="E84" s="5" t="s">
-        <v>192</v>
+        <v>179</v>
       </c>
       <c r="F84" s="4" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="G84" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H84" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="85" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A85" s="7">
         <v>82</v>
       </c>
-      <c r="B85" s="7" t="s">
-        <v>193</v>
-      </c>
+      <c r="B85" s="7"/>
       <c r="C85" s="7">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D85" s="7" t="s">
-        <v>194</v>
+        <v>180</v>
       </c>
       <c r="E85" s="8" t="s">
-        <v>195</v>
+        <v>181</v>
       </c>
       <c r="F85" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G85" s="9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H85" s="7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="86" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A86" s="4">
         <v>83</v>
       </c>
-      <c r="B86" s="4" t="s">
-        <v>193</v>
-      </c>
+      <c r="B86" s="4"/>
       <c r="C86" s="4">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D86" s="4" t="s">
-        <v>196</v>
+        <v>182</v>
       </c>
       <c r="E86" s="5" t="s">
-        <v>197</v>
+        <v>183</v>
       </c>
       <c r="F86" s="4" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="G86" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H86" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="87" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A87" s="7">
         <v>84</v>
       </c>
-      <c r="B87" s="7" t="s">
-        <v>193</v>
-      </c>
+      <c r="B87" s="7"/>
       <c r="C87" s="7">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="D87" s="7" t="s">
-        <v>198</v>
+        <v>184</v>
       </c>
       <c r="E87" s="8" t="s">
-        <v>199</v>
+        <v>185</v>
       </c>
       <c r="F87" s="7" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G87" s="9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H87" s="7" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="88" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A88" s="4">
-        <v>85</v>
-      </c>
-      <c r="B88" s="4" t="s">
-        <v>193</v>
-      </c>
-      <c r="C88" s="4">
-        <v>20</v>
-      </c>
-      <c r="D88" s="4" t="s">
-        <v>200</v>
-      </c>
-      <c r="E88" s="5" t="s">
-        <v>201</v>
-      </c>
-      <c r="F88" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="G88" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="H88" s="4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="89" ht="26" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A89" s="10" t="s">
-        <v>202</v>
-      </c>
-      <c r="B89" s="10"/>
-      <c r="C89" s="10"/>
-      <c r="D89" s="10"/>
-      <c r="E89" s="11" t="s">
-        <v>203</v>
-      </c>
-      <c r="F89" s="12" t="s">
-        <v>204</v>
-      </c>
-      <c r="G89" s="12" t="s">
-        <v>204</v>
-      </c>
-      <c r="H89" s="12" t="s">
-        <v>204</v>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="88" ht="26" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A88" s="10" t="s">
+        <v>186</v>
+      </c>
+      <c r="B88" s="10"/>
+      <c r="C88" s="10"/>
+      <c r="D88" s="10"/>
+      <c r="E88" s="11" t="s">
+        <v>187</v>
+      </c>
+      <c r="F88" s="12" t="s">
+        <v>188</v>
+      </c>
+      <c r="G88" s="12" t="s">
+        <v>188</v>
+      </c>
+      <c r="H88" s="12" t="s">
+        <v>188</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A89:D89"/>
+    <mergeCell ref="A88:D88"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
